--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119822724</v>
       </c>
       <c r="B2" t="n">
-        <v>57421</v>
+        <v>57431</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,152 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129673488</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57834</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Offerberget, Mellbomyran Arbrå, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>561305</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6820679</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observerade par i lämplig biotop med skiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Skiktad granskog med god slutenhet</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129673488</v>
       </c>
       <c r="B3" t="n">
-        <v>57834</v>
+        <v>57839</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129673488</v>
       </c>
       <c r="B3" t="n">
-        <v>57839</v>
+        <v>57840</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,6 +929,129 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129805055</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57568</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102622</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pärluggla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aegolius funereus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ringmärktes</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mellbomyran NO, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>561268</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6820635</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Englund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Englund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>129805055</v>
       </c>
       <c r="B4" t="n">
-        <v>57568</v>
+        <v>57569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129673488</v>
       </c>
       <c r="B3" t="n">
-        <v>57840</v>
+        <v>57841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129673488</v>
       </c>
       <c r="B3" t="n">
-        <v>57841</v>
+        <v>57844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>129805055</v>
       </c>
       <c r="B4" t="n">
-        <v>57569</v>
+        <v>57572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129673488</v>
       </c>
       <c r="B3" t="n">
-        <v>57845</v>
+        <v>57930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>129673488</v>
       </c>
       <c r="B3" t="n">
-        <v>57930</v>
+        <v>57956</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -934,7 +934,7 @@
         <v>129805055</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57718</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,61 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119822724</v>
+        <v>118676871</v>
       </c>
       <c r="B2" t="n">
-        <v>57431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellbomyran NO, Hls</t>
+          <t>Galven, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561268</v>
+        <v>561128</v>
       </c>
       <c r="R2" t="n">
-        <v>6820635</v>
+        <v>6820670</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,12 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,39 +769,39 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Åke Englund</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Åke Englund</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129673488</v>
+        <v>129805055</v>
       </c>
       <c r="B3" t="n">
-        <v>57956</v>
+        <v>57785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>102622</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,37 +816,29 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1K</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>ringmärktes</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Offerberget, Mellbomyran Arbrå, Hls</t>
+          <t>Mellbomyran NO, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561305</v>
+        <v>561268</v>
       </c>
       <c r="R3" t="n">
-        <v>6820679</v>
+        <v>6820635</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,27 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Observerade par i lämplig biotop med skiktad granskog.</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,53 +888,43 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Skiktad granskog med god slutenhet</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Minnefors</t>
+          <t>Åke Englund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Minnefors</t>
+          <t>Åke Englund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129805055</v>
+        <v>107152089</v>
       </c>
       <c r="B4" t="n">
-        <v>57718</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102622</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -964,28 +937,20 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1K</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>ringmärktes</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellbomyran NO, Hls</t>
+          <t>Mellbomyran, Mellbomyran Arbrå, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561268</v>
+        <v>560975</v>
       </c>
       <c r="R4" t="n">
-        <v>6820635</v>
+        <v>6820565</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1012,22 +977,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,15 +1007,381 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Erik Söderlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Söderlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>107152152</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mellbomyran, Mellbomyran Arbrå, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>561334</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6820596</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-11-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Söderlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Söderlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119822724</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellbomyran NO, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>561268</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6820635</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Åke Englund</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Åke Englund</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129673488</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Offerberget, Mellbomyran Arbrå, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>561305</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6820679</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Observerade par i lämplig biotop med skiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Skiktad granskog med god slutenhet</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676871</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805055</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107152089</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107152152</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119822724</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,8 +1412,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129673488</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,27 +919,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107152089</v>
+        <v>136443683</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>58149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>103023</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -953,22 +953,26 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mellbomyran, Mellbomyran Arbrå, Hls</t>
+          <t>Mellbo, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560975</v>
+        <v>561220</v>
       </c>
       <c r="R4" t="n">
-        <v>6820565</v>
+        <v>6820621</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +996,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1022,24 +1026,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Söderlund</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Söderlund</t>
+          <t>Anita Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107152089</t>
+          <t>https://artportalen.se/Sighting/136443683</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107152152</v>
+        <v>107152089</v>
       </c>
       <c r="B5" t="n">
         <v>58057</v>
@@ -1082,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561334</v>
+        <v>560975</v>
       </c>
       <c r="R5" t="n">
-        <v>6820596</v>
+        <v>6820565</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,22 +1116,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-11</t>
+          <t>2022-10-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-24</t>
+          <t>2022-11-09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,13 +1157,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/107152152</t>
+          <t>https://artportalen.se/Sighting/107152089</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119822724</v>
+        <v>107152152</v>
       </c>
       <c r="B6" t="n">
         <v>58057</v>
@@ -1189,7 +1193,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1198,14 +1202,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mellbomyran NO, Hls</t>
+          <t>Mellbomyran, Mellbomyran Arbrå, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561268</v>
+        <v>561334</v>
       </c>
       <c r="R6" t="n">
-        <v>6820635</v>
+        <v>6820596</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,12 +1236,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-15</t>
+          <t>2022-11-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,24 +1266,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Åke Englund</t>
+          <t>Erik Söderlund</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åke Englund</t>
+          <t>Erik Söderlund</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119822724</t>
+          <t>https://artportalen.se/Sighting/107152152</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129673488</v>
+        <v>119822724</v>
       </c>
       <c r="B7" t="n">
         <v>58057</v>
@@ -1299,42 +1313,26 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Offerberget, Mellbomyran Arbrå, Hls</t>
+          <t>Mellbomyran NO, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561305</v>
+        <v>561268</v>
       </c>
       <c r="R7" t="n">
-        <v>6820679</v>
+        <v>6820635</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,27 +1356,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observerade par i lämplig biotop med skiktad granskog.</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1389,32 +1372,289 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Skiktad granskog med god slutenhet</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Minnefors</t>
+          <t>Åke Englund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Minnefors</t>
+          <t>Åke Englund</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/119822724</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129673488</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Offerberget, Mellbomyran Arbrå, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>561305</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6820679</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Observerade par i lämplig biotop med skiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skiktad granskog med god slutenhet</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Minnefors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/129673488</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136444139</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99328</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellbo, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>561030</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6820531</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bollnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Arbrå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anita Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anita Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136444139</t>
         </is>
       </c>
     </row>
@@ -1426,6 +1666,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -922,7 +922,7 @@
         <v>136443683</v>
       </c>
       <c r="B4" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 38971-2024 artfynd.xlsx
+++ b/artfynd/A 38971-2024 artfynd.xlsx
@@ -1547,7 +1547,7 @@
         <v>136444139</v>
       </c>
       <c r="B9" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
